--- a/static/uploads/excel_data.xlsx
+++ b/static/uploads/excel_data.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonProject\koco_final\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5214B6-9A5D-4F8A-8D55-9EFF8E9AB4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{982D17C5-39C0-40CD-811C-744AC771A250}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9" yWindow="9" windowWidth="32897" windowHeight="17897" xr2:uid="{A0E89E0C-3C05-401B-9D24-E353635E5843}"/>
+    <workbookView xWindow="825" yWindow="0" windowWidth="27630" windowHeight="15600" xr2:uid="{FEC051BA-7B85-4BE1-808E-959DB3CC53EA}"/>
   </bookViews>
   <sheets>
     <sheet name="VCeph Analysis" sheetId="1" r:id="rId1"/>
@@ -26,8 +21,6 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,36 +28,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>OPDA</t>
   </si>
   <si>
-    <t>(Female IIA)</t>
+    <t>(Female Adults)</t>
   </si>
   <si>
     <t>ID :</t>
   </si>
   <si>
-    <t>Birth :</t>
-  </si>
-  <si>
-    <t>2013.01.04</t>
-  </si>
-  <si>
-    <t>NAME :</t>
-  </si>
-  <si>
-    <t>AGE :</t>
-  </si>
-  <si>
-    <t>9y 6m</t>
-  </si>
-  <si>
-    <t>GENDER :</t>
-  </si>
-  <si>
-    <t>DATE :</t>
+    <t>Patient0002</t>
+  </si>
+  <si>
+    <t>생년월일 :</t>
+  </si>
+  <si>
+    <t>1981.12.23</t>
+  </si>
+  <si>
+    <t>이름 :</t>
+  </si>
+  <si>
+    <t>김주리</t>
+  </si>
+  <si>
+    <t>나이 :</t>
+  </si>
+  <si>
+    <t>40y 8m</t>
+  </si>
+  <si>
+    <t>성별 :</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>날짜 :</t>
+  </si>
+  <si>
+    <t>2022.08.16</t>
   </si>
   <si>
     <t>Measurement</t>
@@ -197,18 +202,6 @@
   </si>
   <si>
     <t>ODI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 옥수수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Male</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.01.28</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -300,7 +293,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -321,9 +314,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -361,7 +354,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -467,7 +460,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -609,92 +602,92 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E143A-6AA5-4343-A167-2E4840B003DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A45BBE0-62F4-4DB6-B7D1-AAB96ABD2CEB}">
   <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.2109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.2109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" ht="33.75" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>220490</v>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -703,26 +696,26 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>81.25</v>
+        <v>81.08</v>
       </c>
       <c r="C10">
-        <v>2.88</v>
+        <v>3.73</v>
       </c>
       <c r="D10">
-        <v>79.31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>74.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -731,26 +724,26 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>77.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>72.150000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>58.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>54.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -759,12 +752,12 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>94.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>91.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -773,12 +766,12 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>27.41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -787,12 +780,12 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>26.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>30.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -801,12 +794,12 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>72.819999999999993</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>65.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -815,12 +808,12 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>94.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>118.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -829,12 +822,12 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -843,12 +836,12 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>82.94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>74.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -857,12 +850,12 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>79.77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>80.489999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0.4</v>
@@ -871,12 +864,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D21">
-        <v>-5.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>-3.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>61.01</v>
@@ -885,40 +878,40 @@
         <v>2.8</v>
       </c>
       <c r="D22">
-        <v>63.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>64.58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23">
-        <v>128.56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>134.85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B24">
-        <v>123</v>
+        <v>125.9</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D24">
-        <v>122.81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>129.77000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -927,12 +920,12 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>1.2</v>
@@ -941,82 +934,82 @@
         <v>4.72</v>
       </c>
       <c r="D26">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>33.520000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>31.94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>57.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>62.29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
         <v>33</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>34.700000000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>40.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>57.04</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>62.79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D31">
-        <v>30.54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>26.69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1025,26 +1018,26 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>48.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>41.83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B33">
-        <v>42</v>
+        <v>51.6</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="D33">
-        <v>35.78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>38.32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1053,12 +1046,12 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>64.61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>55.62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1067,12 +1060,12 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>65.930000000000007</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>67.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>53.4</v>
@@ -1081,26 +1074,26 @@
         <v>3.5</v>
       </c>
       <c r="D36">
-        <v>51.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>47.68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B37">
-        <v>71.13</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37">
-        <v>72.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>69.819999999999993</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1109,40 +1102,40 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>6.26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B39">
-        <v>51.06</v>
+        <v>46.2</v>
       </c>
       <c r="C39">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="D39">
-        <v>49.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>48.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B40">
-        <v>77.8</v>
+        <v>78.040000000000006</v>
       </c>
       <c r="C40">
-        <v>2.91</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D40">
-        <v>70.569999999999993</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>80.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1151,12 +1144,12 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>50.28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>67.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1165,12 +1158,12 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>11.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>18.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1179,12 +1172,12 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>91.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B44">
         <v>2.2999999999999998</v>
@@ -1193,12 +1186,12 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>3.2</v>
@@ -1207,12 +1200,12 @@
         <v>2</v>
       </c>
       <c r="D45">
-        <v>6.89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B46">
         <v>85.74</v>
@@ -1221,12 +1214,12 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="D46">
-        <v>81.17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>84.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1235,12 +1228,12 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>74.22</v>
+        <v>69.17</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/static/uploads/excel_data.xlsx
+++ b/static/uploads/excel_data.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{982D17C5-39C0-40CD-811C-744AC771A250}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonProject\koco_final\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5214B6-9A5D-4F8A-8D55-9EFF8E9AB4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="0" windowWidth="27630" windowHeight="15600" xr2:uid="{FEC051BA-7B85-4BE1-808E-959DB3CC53EA}"/>
+    <workbookView xWindow="9" yWindow="9" windowWidth="32897" windowHeight="17897" xr2:uid="{A0E89E0C-3C05-401B-9D24-E353635E5843}"/>
   </bookViews>
   <sheets>
     <sheet name="VCeph Analysis" sheetId="1" r:id="rId1"/>
@@ -21,6 +26,8 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,48 +35,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>OPDA</t>
   </si>
   <si>
-    <t>(Female Adults)</t>
+    <t>(Female IIA)</t>
   </si>
   <si>
     <t>ID :</t>
   </si>
   <si>
-    <t>Patient0002</t>
-  </si>
-  <si>
-    <t>생년월일 :</t>
-  </si>
-  <si>
-    <t>1981.12.23</t>
-  </si>
-  <si>
-    <t>이름 :</t>
-  </si>
-  <si>
-    <t>김주리</t>
-  </si>
-  <si>
-    <t>나이 :</t>
-  </si>
-  <si>
-    <t>40y 8m</t>
-  </si>
-  <si>
-    <t>성별 :</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>날짜 :</t>
-  </si>
-  <si>
-    <t>2022.08.16</t>
+    <t>Birth :</t>
+  </si>
+  <si>
+    <t>2013.01.04</t>
+  </si>
+  <si>
+    <t>NAME :</t>
+  </si>
+  <si>
+    <t>AGE :</t>
+  </si>
+  <si>
+    <t>9y 6m</t>
+  </si>
+  <si>
+    <t>GENDER :</t>
+  </si>
+  <si>
+    <t>DATE :</t>
   </si>
   <si>
     <t>Measurement</t>
@@ -202,6 +197,18 @@
   </si>
   <si>
     <t>ODI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 옥수수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Male</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.01.28</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -293,7 +300,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -314,9 +321,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -354,7 +361,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -460,7 +467,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,260 +609,260 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A45BBE0-62F4-4DB6-B7D1-AAB96ABD2CEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E143A-6AA5-4343-A167-2E4840B003DE}">
   <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.2109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.2109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="31.3" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>220490</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B10">
+        <v>81.25</v>
+      </c>
+      <c r="C10">
+        <v>2.88</v>
+      </c>
+      <c r="D10">
+        <v>79.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>77.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B12">
+        <v>62.5</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>58.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>94.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
-        <v>81.08</v>
-      </c>
-      <c r="C10">
-        <v>3.73</v>
-      </c>
-      <c r="D10">
-        <v>74.34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>27.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>72.150000000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>26.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>54.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>72.819999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>91.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>94.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
         <v>24</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>30.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>82.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>65.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>79.77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
         <v>26</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>118.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>74.66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>80.489999999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>30</v>
       </c>
       <c r="B21">
         <v>0.4</v>
@@ -864,12 +871,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D21">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-5.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>61.01</v>
@@ -878,54 +885,54 @@
         <v>2.8</v>
       </c>
       <c r="D22">
-        <v>64.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>128.56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24">
+        <v>123</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>122.81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
         <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23">
-        <v>134.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24">
-        <v>125.9</v>
-      </c>
-      <c r="C24">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D24">
-        <v>129.77000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>12.06</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>36</v>
       </c>
       <c r="B26">
         <v>1.2</v>
@@ -934,138 +941,138 @@
         <v>4.72</v>
       </c>
       <c r="D26">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>40.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>57.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>62.79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
         <v>37</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>33.520000000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31">
+        <v>30.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>38</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>31.94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>48.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>57.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B33">
+        <v>42</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>35.78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>62.29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>64.61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
         <v>41</v>
       </c>
-      <c r="B31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31">
-        <v>26.69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>65.930000000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
         <v>42</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>41.83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33">
-        <v>51.6</v>
-      </c>
-      <c r="C33">
-        <v>4.2</v>
-      </c>
-      <c r="D33">
-        <v>38.32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>55.62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>67.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>46</v>
       </c>
       <c r="B36">
         <v>53.4</v>
@@ -1074,110 +1081,110 @@
         <v>3.5</v>
       </c>
       <c r="D36">
-        <v>47.68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>51.12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B37">
-        <v>76</v>
+        <v>71.13</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37">
-        <v>69.819999999999993</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>72.19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39">
+        <v>51.06</v>
+      </c>
+      <c r="C39">
+        <v>2.85</v>
+      </c>
+      <c r="D39">
+        <v>49.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>77.8</v>
+      </c>
+      <c r="C40">
+        <v>2.91</v>
+      </c>
+      <c r="D40">
+        <v>70.569999999999993</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>50.28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
         <v>48</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
         <v>49</v>
       </c>
-      <c r="B39">
-        <v>46.2</v>
-      </c>
-      <c r="C39">
-        <v>3.26</v>
-      </c>
-      <c r="D39">
-        <v>48.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>91.08</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
         <v>50</v>
-      </c>
-      <c r="B40">
-        <v>78.040000000000006</v>
-      </c>
-      <c r="C40">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D40">
-        <v>80.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>67.06</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>18.22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>54</v>
       </c>
       <c r="B44">
         <v>2.2999999999999998</v>
@@ -1186,12 +1193,12 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>3.2</v>
@@ -1200,12 +1207,12 @@
         <v>2</v>
       </c>
       <c r="D45">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B46">
         <v>85.74</v>
@@ -1214,12 +1221,12 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="D46">
-        <v>84.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>81.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1228,12 +1235,12 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>69.17</v>
+        <v>74.22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>